--- a/config/prioridad_tiendas.ejemplo.xlsx
+++ b/config/prioridad_tiendas.ejemplo.xlsx
@@ -7020,7 +7020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7167,32 +7167,66 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>max_unidades_por_tienda</t>
+          <t>reserva_por_tienda</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tope de unidades reasignadas por tienda en una corrida. 0 = sin tope.</t>
+          <t>Unidades que deberia conservar la tienda despues de ceder. Con 1, se evita dejarla en cero; si ninguna tienda puede conservarlas, recien ahi se acepta la ultima unidad. 0 desactiva la regla.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>ordenar_por_stock</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SI = dentro de la misma banda de prioridad gana la tienda con mas stock. NO = gana la primera de la lista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>max_unidades_por_tienda</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tope de unidades reasignadas por tienda en una corrida. 0 = sin tope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>columna_salida</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Nom Tda Reasignada</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Nombre exacto de la columna donde se escribe la tienda reasignada.</t>
         </is>
